--- a/anatoliachalcolithicsitesgeocoords.xlsx
+++ b/anatoliachalcolithicsitesgeocoords.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amiottm/Documents/ARCHY208/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evijonas/python/archyviz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92706981-7069-BE46-A9B4-F5644229468B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E914658-334A-784B-8444-58016E76ACCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="3760" windowWidth="30920" windowHeight="15680" xr2:uid="{6D9CE6C4-E000-5C47-BF09-314953C46AD5}"/>
+    <workbookView xWindow="0" yWindow="3440" windowWidth="29400" windowHeight="15680" xr2:uid="{6D9CE6C4-E000-5C47-BF09-314953C46AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
